--- a/data/community-listings.xlsx
+++ b/data/community-listings.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4081" uniqueCount="1253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4091" uniqueCount="1254">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -1849,10 +1849,13 @@
     <t xml:space="preserve">30 Bali Lane</t>
   </si>
   <si>
+    <t xml:space="preserve">189866</t>
+  </si>
+  <si>
     <t xml:space="preserve">Indonesian, Noodle</t>
   </si>
   <si>
-    <t xml:space="preserve">Source: OpenStreetMap (© OpenStreetMap contributors, ODbL). OSM record last updated 2025-04-17.</t>
+    <t xml:space="preserve">Source: OpenStreetMap (© OpenStreetMap contributors, ODbL). OSM record last updated 2025-04-17. Postal code from OneMap, Singapore Land Authority, under the Singapore Open Data Licence v1.0.</t>
   </si>
   <si>
     <t xml:space="preserve">https://kulonsingapore.com/</t>
@@ -1901,9 +1904,6 @@
   </si>
   <si>
     <t xml:space="preserve">Seafood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Source: OpenStreetMap (© OpenStreetMap contributors, ODbL). OSM record last updated 2025-04-17. Postal code from OneMap, Singapore Land Authority, under the Singapore Open Data Licence v1.0.</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.longjohnsilvers.com.sg/</t>
@@ -2314,7 +2314,7 @@
     <t xml:space="preserve">Dessert</t>
   </si>
   <si>
-    <t xml:space="preserve">Source: OpenStreetMap (© OpenStreetMap contributors, ODbL). OSM record last updated 2024-04-21.</t>
+    <t xml:space="preserve">Source: OpenStreetMap (© OpenStreetMap contributors, ODbL). OSM record last updated 2024-04-21. Postal code from OneMap, Singapore Land Authority, under the Singapore Open Data Licence v1.0.</t>
   </si>
   <si>
     <t xml:space="preserve">com-74853357</t>
@@ -2402,6 +2402,9 @@
   </si>
   <si>
     <t xml:space="preserve">Ramen, Indonesian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source: OpenStreetMap (© OpenStreetMap contributors, ODbL). OSM record last updated 2025-04-17.</t>
   </si>
   <si>
     <t xml:space="preserve">com-416f7ec3</t>
@@ -12628,12 +12631,24 @@
       <c r="D97" s="1" t="s">
         <v>607</v>
       </c>
+      <c r="E97" s="1" t="s">
+        <v>608</v>
+      </c>
       <c r="F97" s="1" t="str">
         <f aca="false">IF(C97="Singapore",IF(LEN(TEXT(E97,"000000"))=6,LEFT(TEXT(E97,"000000"),2),""),"")</f>
-        <v>00</v>
+        <v>18</v>
+      </c>
+      <c r="H97" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="I97" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="J97" s="1" t="s">
+        <v>224</v>
       </c>
       <c r="K97" s="11" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="L97" s="11" t="s">
         <v>59</v>
@@ -12660,13 +12675,13 @@
         <v>63</v>
       </c>
       <c r="AK97" s="1" t="s">
-        <v>609</v>
-      </c>
-      <c r="AM97" s="12" t="n">
-        <v>46311</v>
+        <v>610</v>
+      </c>
+      <c r="AM97" s="12" t="s">
+        <v>65</v>
       </c>
       <c r="AN97" s="1" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AT97" s="1" t="s">
         <v>66</v>
@@ -12690,19 +12705,19 @@
     </row>
     <row r="98" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="1" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C98" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="F98" s="1" t="str">
         <f aca="false">IF(C98="Singapore",IF(LEN(TEXT(E98,"000000"))=6,LEFT(TEXT(E98,"000000"),2),""),"")</f>
@@ -12718,7 +12733,7 @@
         <v>224</v>
       </c>
       <c r="K98" s="11" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="L98" s="11" t="s">
         <v>59</v>
@@ -12745,13 +12760,13 @@
         <v>63</v>
       </c>
       <c r="AK98" s="1" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="AM98" s="12" t="n">
         <v>46311</v>
       </c>
       <c r="AN98" s="1" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AT98" s="1" t="s">
         <v>66</v>
@@ -12775,10 +12790,10 @@
     </row>
     <row r="99" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="1" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C99" s="11" t="s">
         <v>52</v>
@@ -12836,7 +12851,7 @@
         <v>46311</v>
       </c>
       <c r="AN99" s="1" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="AT99" s="1" t="s">
         <v>66</v>
@@ -12860,19 +12875,19 @@
     </row>
     <row r="100" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="1" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C100" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="F100" s="1" t="str">
         <f aca="false">IF(C100="Singapore",IF(LEN(TEXT(E100,"000000"))=6,LEFT(TEXT(E100,"000000"),2),""),"")</f>
@@ -12888,7 +12903,7 @@
         <v>89</v>
       </c>
       <c r="K100" s="11" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="L100" s="11" t="s">
         <v>59</v>
@@ -12915,7 +12930,7 @@
         <v>63</v>
       </c>
       <c r="AK100" s="1" t="s">
-        <v>626</v>
+        <v>610</v>
       </c>
       <c r="AM100" s="12" t="s">
         <v>65</v>
@@ -12948,7 +12963,7 @@
         <v>628</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C101" s="11" t="s">
         <v>52</v>
@@ -12973,7 +12988,7 @@
         <v>72</v>
       </c>
       <c r="K101" s="11" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="L101" s="11" t="s">
         <v>59</v>
@@ -15596,9 +15611,21 @@
       <c r="D134" s="1" t="s">
         <v>755</v>
       </c>
+      <c r="E134" s="1" t="s">
+        <v>475</v>
+      </c>
       <c r="F134" s="1" t="str">
         <f aca="false">IF(C134="Singapore",IF(LEN(TEXT(E134,"000000"))=6,LEFT(TEXT(E134,"000000"),2),""),"")</f>
-        <v>00</v>
+        <v>43</v>
+      </c>
+      <c r="H134" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="I134" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="J134" s="1" t="s">
+        <v>269</v>
       </c>
       <c r="K134" s="11" t="s">
         <v>756</v>
@@ -15630,8 +15657,8 @@
       <c r="AK134" s="1" t="s">
         <v>757</v>
       </c>
-      <c r="AM134" s="12" t="n">
-        <v>46311</v>
+      <c r="AM134" s="12" t="s">
+        <v>65</v>
       </c>
       <c r="AT134" s="1" t="s">
         <v>66</v>
@@ -16127,7 +16154,7 @@
         <v>63</v>
       </c>
       <c r="AK140" s="1" t="s">
-        <v>609</v>
+        <v>787</v>
       </c>
       <c r="AM140" s="12" t="n">
         <v>46311</v>
@@ -16154,10 +16181,10 @@
     </row>
     <row r="141" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A141" s="1" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="C141" s="11" t="s">
         <v>52</v>
@@ -16166,7 +16193,7 @@
         <v>77</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="F141" s="1" t="str">
         <f aca="false">IF(C141="Singapore",IF(LEN(TEXT(E141,"000000"))=6,LEFT(TEXT(E141,"000000"),2),""),"")</f>
@@ -16182,7 +16209,7 @@
         <v>72</v>
       </c>
       <c r="K141" s="11" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="L141" s="11" t="s">
         <v>59</v>
@@ -16215,7 +16242,7 @@
         <v>46311</v>
       </c>
       <c r="AN141" s="1" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="AT141" s="1" t="s">
         <v>66</v>
@@ -16239,19 +16266,19 @@
     </row>
     <row r="142" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A142" s="1" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="C142" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="F142" s="1" t="str">
         <f aca="false">IF(C142="Singapore",IF(LEN(TEXT(E142,"000000"))=6,LEFT(TEXT(E142,"000000"),2),""),"")</f>
@@ -16292,7 +16319,7 @@
         <v>63</v>
       </c>
       <c r="AK142" s="1" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="AM142" s="12" t="s">
         <v>65</v>
@@ -16319,10 +16346,10 @@
     </row>
     <row r="143" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A143" s="1" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="C143" s="11" t="s">
         <v>52</v>
@@ -16401,16 +16428,16 @@
     </row>
     <row r="144" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A144" s="1" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="C144" s="11" t="s">
         <v>52</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="F144" s="1" t="str">
         <f aca="false">IF(C144="Singapore",IF(LEN(TEXT(E144,"000000"))=6,LEFT(TEXT(E144,"000000"),2),""),"")</f>
@@ -16426,7 +16453,7 @@
         <v>224</v>
       </c>
       <c r="K144" s="11" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="L144" s="11" t="s">
         <v>59</v>
@@ -16453,13 +16480,13 @@
         <v>63</v>
       </c>
       <c r="AK144" s="1" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="AM144" s="12" t="n">
         <v>46311</v>
       </c>
       <c r="AN144" s="1" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="AT144" s="1" t="s">
         <v>66</v>
@@ -16483,19 +16510,19 @@
     </row>
     <row r="145" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A145" s="1" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C145" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="F145" s="1" t="str">
         <f aca="false">IF(C145="Singapore",IF(LEN(TEXT(E145,"000000"))=6,LEFT(TEXT(E145,"000000"),2),""),"")</f>
@@ -16544,7 +16571,7 @@
         <v>46311</v>
       </c>
       <c r="AN145" s="1" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="AT145" s="1" t="s">
         <v>66</v>
@@ -16568,16 +16595,16 @@
     </row>
     <row r="146" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A146" s="1" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="C146" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="E146" s="1" t="s">
         <v>662</v>
@@ -16596,7 +16623,7 @@
         <v>89</v>
       </c>
       <c r="K146" s="11" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="L146" s="11" t="s">
         <v>59</v>
@@ -16629,7 +16656,7 @@
         <v>46311</v>
       </c>
       <c r="AN146" s="1" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="AT146" s="1" t="s">
         <v>66</v>
@@ -16653,19 +16680,19 @@
     </row>
     <row r="147" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A147" s="1" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="C147" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="F147" s="1" t="str">
         <f aca="false">IF(C147="Singapore",IF(LEN(TEXT(E147,"000000"))=6,LEFT(TEXT(E147,"000000"),2),""),"")</f>
@@ -16735,19 +16762,19 @@
     </row>
     <row r="148" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A148" s="1" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="C148" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="F148" s="1" t="str">
         <f aca="false">IF(C148="Singapore",IF(LEN(TEXT(E148,"000000"))=6,LEFT(TEXT(E148,"000000"),2),""),"")</f>
@@ -16790,13 +16817,13 @@
         <v>63</v>
       </c>
       <c r="AK148" s="1" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="AM148" s="12" t="n">
         <v>46311</v>
       </c>
       <c r="AN148" s="1" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="AT148" s="1" t="s">
         <v>66</v>
@@ -16820,32 +16847,32 @@
     </row>
     <row r="149" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A149" s="1" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="C149" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="F149" s="1" t="str">
         <f aca="false">IF(C149="Singapore",IF(LEN(TEXT(E149,"000000"))=6,LEFT(TEXT(E149,"000000"),2),""),"")</f>
         <v>79</v>
       </c>
       <c r="H149" s="1" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="I149" s="1" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="J149" s="1" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="K149" s="11" t="s">
         <v>58</v>
@@ -16875,13 +16902,13 @@
         <v>63</v>
       </c>
       <c r="AK149" s="1" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="AM149" s="12" t="n">
         <v>46311</v>
       </c>
       <c r="AN149" s="1" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="AT149" s="1" t="s">
         <v>66</v>
@@ -16905,10 +16932,10 @@
     </row>
     <row r="150" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A150" s="1" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="C150" s="11" t="s">
         <v>52</v>
@@ -16933,7 +16960,7 @@
         <v>72</v>
       </c>
       <c r="K150" s="11" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="L150" s="11" t="s">
         <v>59</v>
@@ -16960,13 +16987,13 @@
         <v>63</v>
       </c>
       <c r="AK150" s="1" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="AM150" s="12" t="n">
         <v>46311</v>
       </c>
       <c r="AN150" s="1" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="AT150" s="1" t="s">
         <v>66</v>
@@ -16990,16 +17017,16 @@
     </row>
     <row r="151" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A151" s="1" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="C151" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="F151" s="1" t="str">
         <f aca="false">IF(C151="Singapore",IF(LEN(TEXT(E151,"000000"))=6,LEFT(TEXT(E151,"000000"),2),""),"")</f>
@@ -17031,7 +17058,7 @@
         <v>63</v>
       </c>
       <c r="AK151" s="1" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="AM151" s="12" t="n">
         <v>46311</v>
@@ -17058,10 +17085,10 @@
     </row>
     <row r="152" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A152" s="1" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="C152" s="11" t="s">
         <v>52</v>
@@ -17113,13 +17140,13 @@
         <v>63</v>
       </c>
       <c r="AK152" s="1" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="AM152" s="12" t="n">
         <v>46311</v>
       </c>
       <c r="AN152" s="1" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="AT152" s="1" t="s">
         <v>66</v>
@@ -17143,19 +17170,19 @@
     </row>
     <row r="153" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A153" s="1" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="C153" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="F153" s="1" t="str">
         <f aca="false">IF(C153="Singapore",IF(LEN(TEXT(E153,"000000"))=6,LEFT(TEXT(E153,"000000"),2),""),"")</f>
@@ -17171,7 +17198,7 @@
         <v>72</v>
       </c>
       <c r="K153" s="11" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="L153" s="11" t="s">
         <v>59</v>
@@ -17198,13 +17225,13 @@
         <v>63</v>
       </c>
       <c r="AK153" s="1" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="AM153" s="12" t="n">
         <v>46311</v>
       </c>
       <c r="AN153" s="1" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="AT153" s="1" t="s">
         <v>66</v>
@@ -17228,19 +17255,19 @@
     </row>
     <row r="154" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A154" s="1" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="C154" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="F154" s="1" t="str">
         <f aca="false">IF(C154="Singapore",IF(LEN(TEXT(E154,"000000"))=6,LEFT(TEXT(E154,"000000"),2),""),"")</f>
@@ -17283,13 +17310,13 @@
         <v>63</v>
       </c>
       <c r="AK154" s="1" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="AM154" s="12" t="n">
         <v>46311</v>
       </c>
       <c r="AN154" s="1" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="AT154" s="1" t="s">
         <v>66</v>
@@ -17313,16 +17340,16 @@
     </row>
     <row r="155" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A155" s="1" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="C155" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="F155" s="1" t="str">
         <f aca="false">IF(C155="Singapore",IF(LEN(TEXT(E155,"000000"))=6,LEFT(TEXT(E155,"000000"),2),""),"")</f>
@@ -17381,19 +17408,19 @@
     </row>
     <row r="156" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A156" s="1" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="C156" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="F156" s="1" t="str">
         <f aca="false">IF(C156="Singapore",IF(LEN(TEXT(E156,"000000"))=6,LEFT(TEXT(E156,"000000"),2),""),"")</f>
@@ -17436,7 +17463,7 @@
         <v>63</v>
       </c>
       <c r="AK156" s="1" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="AM156" s="12" t="n">
         <v>46311</v>
@@ -17463,19 +17490,19 @@
     </row>
     <row r="157" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A157" s="1" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="C157" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="F157" s="1" t="str">
         <f aca="false">IF(C157="Singapore",IF(LEN(TEXT(E157,"000000"))=6,LEFT(TEXT(E157,"000000"),2),""),"")</f>
@@ -17518,13 +17545,13 @@
         <v>63</v>
       </c>
       <c r="AK157" s="1" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="AM157" s="12" t="n">
         <v>46311</v>
       </c>
       <c r="AN157" s="1" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="AT157" s="1" t="s">
         <v>66</v>
@@ -17548,19 +17575,19 @@
     </row>
     <row r="158" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A158" s="1" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="C158" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="F158" s="1" t="str">
         <f aca="false">IF(C158="Singapore",IF(LEN(TEXT(E158,"000000"))=6,LEFT(TEXT(E158,"000000"),2),""),"")</f>
@@ -17603,13 +17630,13 @@
         <v>63</v>
       </c>
       <c r="AK158" s="1" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="AM158" s="12" t="n">
         <v>46311</v>
       </c>
       <c r="AN158" s="1" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="AT158" s="1" t="s">
         <v>66</v>
@@ -17633,10 +17660,10 @@
     </row>
     <row r="159" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A159" s="1" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="C159" s="11" t="s">
         <v>52</v>
@@ -17694,7 +17721,7 @@
         <v>46311</v>
       </c>
       <c r="AN159" s="1" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="AT159" s="1" t="s">
         <v>66</v>
@@ -17718,19 +17745,19 @@
     </row>
     <row r="160" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A160" s="1" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="C160" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="F160" s="1" t="str">
         <f aca="false">IF(C160="Singapore",IF(LEN(TEXT(E160,"000000"))=6,LEFT(TEXT(E160,"000000"),2),""),"")</f>
@@ -17773,7 +17800,7 @@
         <v>63</v>
       </c>
       <c r="AK160" s="1" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="AM160" s="12" t="s">
         <v>65</v>
@@ -17800,10 +17827,10 @@
     </row>
     <row r="161" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A161" s="1" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="C161" s="11" t="s">
         <v>52</v>
@@ -17828,7 +17855,7 @@
         <v>72</v>
       </c>
       <c r="K161" s="11" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="L161" s="11" t="s">
         <v>59</v>
@@ -17861,7 +17888,7 @@
         <v>46311</v>
       </c>
       <c r="AN161" s="1" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="AT161" s="1" t="s">
         <v>66</v>
@@ -17885,16 +17912,16 @@
     </row>
     <row r="162" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A162" s="1" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="C162" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="E162" s="1" t="s">
         <v>441</v>
@@ -17940,7 +17967,7 @@
         <v>63</v>
       </c>
       <c r="AK162" s="1" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="AM162" s="12" t="s">
         <v>65</v>
@@ -17967,16 +17994,16 @@
     </row>
     <row r="163" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A163" s="1" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="C163" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="F163" s="1" t="str">
         <f aca="false">IF(C163="Singapore",IF(LEN(TEXT(E163,"000000"))=6,LEFT(TEXT(E163,"000000"),2),""),"")</f>
@@ -18010,7 +18037,7 @@
         <v>63</v>
       </c>
       <c r="AK163" s="1" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="AM163" s="12" t="n">
         <v>46311</v>
@@ -18037,16 +18064,16 @@
     </row>
     <row r="164" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A164" s="1" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="C164" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="F164" s="1" t="str">
         <f aca="false">IF(C164="Singapore",IF(LEN(TEXT(E164,"000000"))=6,LEFT(TEXT(E164,"000000"),2),""),"")</f>
@@ -18107,16 +18134,16 @@
     </row>
     <row r="165" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A165" s="1" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="C165" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="E165" s="1" t="s">
         <v>192</v>
@@ -18135,7 +18162,7 @@
         <v>195</v>
       </c>
       <c r="K165" s="11" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="L165" s="11" t="s">
         <v>59</v>
@@ -18162,7 +18189,7 @@
         <v>63</v>
       </c>
       <c r="AK165" s="1" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="AM165" s="12" t="n">
         <v>46311</v>
@@ -18189,16 +18216,16 @@
     </row>
     <row r="166" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A166" s="1" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="C166" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="E166" s="1" t="s">
         <v>282</v>
@@ -18248,7 +18275,7 @@
         <v>46311</v>
       </c>
       <c r="AN166" s="1" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="AT166" s="1" t="s">
         <v>66</v>
@@ -18272,16 +18299,16 @@
     </row>
     <row r="167" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A167" s="1" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="C167" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="E167" s="1" t="s">
         <v>86</v>
@@ -18325,7 +18352,7 @@
         <v>63</v>
       </c>
       <c r="AK167" s="1" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="AM167" s="12" t="n">
         <v>46311</v>
@@ -18352,19 +18379,19 @@
     </row>
     <row r="168" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A168" s="1" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="C168" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="F168" s="1" t="str">
         <f aca="false">IF(C168="Singapore",IF(LEN(TEXT(E168,"000000"))=6,LEFT(TEXT(E168,"000000"),2),""),"")</f>
@@ -18380,7 +18407,7 @@
         <v>224</v>
       </c>
       <c r="K168" s="11" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="L168" s="11" t="s">
         <v>59</v>
@@ -18407,7 +18434,7 @@
         <v>63</v>
       </c>
       <c r="AK168" s="1" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="AM168" s="12" t="n">
         <v>46311</v>
@@ -18434,19 +18461,19 @@
     </row>
     <row r="169" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A169" s="1" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="C169" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="F169" s="1" t="str">
         <f aca="false">IF(C169="Singapore",IF(LEN(TEXT(E169,"000000"))=6,LEFT(TEXT(E169,"000000"),2),""),"")</f>
@@ -18489,13 +18516,13 @@
         <v>63</v>
       </c>
       <c r="AK169" s="1" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="AM169" s="12" t="n">
         <v>46311</v>
       </c>
       <c r="AN169" s="1" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="AT169" s="1" t="s">
         <v>66</v>
@@ -18519,26 +18546,26 @@
     </row>
     <row r="170" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A170" s="1" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="C170" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="F170" s="1" t="str">
         <f aca="false">IF(C170="Singapore",IF(LEN(TEXT(E170,"000000"))=6,LEFT(TEXT(E170,"000000"),2),""),"")</f>
         <v>30</v>
       </c>
       <c r="H170" s="1" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="I170" s="1" t="s">
         <v>109</v>
@@ -18547,7 +18574,7 @@
         <v>110</v>
       </c>
       <c r="K170" s="11" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="L170" s="11" t="s">
         <v>59</v>
@@ -18574,13 +18601,13 @@
         <v>63</v>
       </c>
       <c r="AK170" s="1" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="AM170" s="12" t="n">
         <v>46311</v>
       </c>
       <c r="AN170" s="1" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="AT170" s="1" t="s">
         <v>66</v>
@@ -18604,32 +18631,32 @@
     </row>
     <row r="171" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A171" s="1" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="C171" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="F171" s="1" t="str">
         <f aca="false">IF(C171="Singapore",IF(LEN(TEXT(E171,"000000"))=6,LEFT(TEXT(E171,"000000"),2),""),"")</f>
         <v>78</v>
       </c>
       <c r="H171" s="1" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="I171" s="1" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="J171" s="1" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="K171" s="11" t="s">
         <v>102</v>
@@ -18659,7 +18686,7 @@
         <v>63</v>
       </c>
       <c r="AK171" s="1" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="AM171" s="12" t="s">
         <v>65</v>
@@ -18686,19 +18713,19 @@
     </row>
     <row r="172" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A172" s="1" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="C172" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="F172" s="1" t="str">
         <f aca="false">IF(C172="Singapore",IF(LEN(TEXT(E172,"000000"))=6,LEFT(TEXT(E172,"000000"),2),""),"")</f>
@@ -18741,13 +18768,13 @@
         <v>63</v>
       </c>
       <c r="AK172" s="1" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="AM172" s="12" t="n">
         <v>46311</v>
       </c>
       <c r="AN172" s="1" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="AT172" s="1" t="s">
         <v>66</v>
@@ -18771,19 +18798,19 @@
     </row>
     <row r="173" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A173" s="1" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="C173" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="F173" s="1" t="str">
         <f aca="false">IF(C173="Singapore",IF(LEN(TEXT(E173,"000000"))=6,LEFT(TEXT(E173,"000000"),2),""),"")</f>
@@ -18826,13 +18853,13 @@
         <v>63</v>
       </c>
       <c r="AK173" s="1" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="AM173" s="12" t="n">
         <v>46311</v>
       </c>
       <c r="AN173" s="1" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="AT173" s="1" t="s">
         <v>66</v>
@@ -18856,10 +18883,10 @@
     </row>
     <row r="174" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A174" s="1" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="C174" s="11" t="s">
         <v>52</v>
@@ -18884,7 +18911,7 @@
         <v>72</v>
       </c>
       <c r="K174" s="11" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="L174" s="11" t="s">
         <v>59</v>
@@ -18917,7 +18944,7 @@
         <v>46311</v>
       </c>
       <c r="AN174" s="1" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="AT174" s="1" t="s">
         <v>66</v>
@@ -18941,26 +18968,26 @@
     </row>
     <row r="175" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A175" s="1" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="C175" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="F175" s="1" t="str">
         <f aca="false">IF(C175="Singapore",IF(LEN(TEXT(E175,"000000"))=6,LEFT(TEXT(E175,"000000"),2),""),"")</f>
         <v>30</v>
       </c>
       <c r="H175" s="1" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="I175" s="1" t="s">
         <v>109</v>
@@ -18969,7 +18996,7 @@
         <v>110</v>
       </c>
       <c r="K175" s="11" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="L175" s="11" t="s">
         <v>59</v>
@@ -18996,7 +19023,7 @@
         <v>63</v>
       </c>
       <c r="AK175" s="1" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="AM175" s="12" t="s">
         <v>65</v>
@@ -19023,19 +19050,19 @@
     </row>
     <row r="176" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A176" s="1" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="C176" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="F176" s="1" t="str">
         <f aca="false">IF(C176="Singapore",IF(LEN(TEXT(E176,"000000"))=6,LEFT(TEXT(E176,"000000"),2),""),"")</f>
@@ -19051,7 +19078,7 @@
         <v>89</v>
       </c>
       <c r="K176" s="11" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="L176" s="11" t="s">
         <v>59</v>
@@ -19078,13 +19105,13 @@
         <v>63</v>
       </c>
       <c r="AK176" s="1" t="s">
-        <v>626</v>
+        <v>610</v>
       </c>
       <c r="AM176" s="12" t="s">
         <v>65</v>
       </c>
       <c r="AN176" s="1" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="AT176" s="1" t="s">
         <v>66</v>
@@ -19108,10 +19135,10 @@
     </row>
     <row r="177" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A177" s="1" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="C177" s="11" t="s">
         <v>52</v>
@@ -19136,7 +19163,7 @@
         <v>57</v>
       </c>
       <c r="K177" s="11" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="L177" s="11" t="s">
         <v>59</v>
@@ -19163,7 +19190,7 @@
         <v>63</v>
       </c>
       <c r="AK177" s="1" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="AM177" s="12" t="s">
         <v>65</v>
@@ -19190,10 +19217,10 @@
     </row>
     <row r="178" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A178" s="1" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="C178" s="11" t="s">
         <v>52</v>
@@ -19218,7 +19245,7 @@
         <v>255</v>
       </c>
       <c r="K178" s="11" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="L178" s="11" t="s">
         <v>59</v>
@@ -19245,7 +19272,7 @@
         <v>63</v>
       </c>
       <c r="AK178" s="1" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="AM178" s="12" t="n">
         <v>46311</v>
@@ -19272,10 +19299,10 @@
     </row>
     <row r="179" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A179" s="1" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="C179" s="11" t="s">
         <v>52</v>
@@ -19300,7 +19327,7 @@
         <v>72</v>
       </c>
       <c r="K179" s="11" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="L179" s="11" t="s">
         <v>59</v>
@@ -19333,7 +19360,7 @@
         <v>46311</v>
       </c>
       <c r="AN179" s="1" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="AT179" s="1" t="s">
         <v>66</v>
@@ -19357,19 +19384,19 @@
     </row>
     <row r="180" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A180" s="1" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="C180" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="F180" s="1" t="str">
         <f aca="false">IF(C180="Singapore",IF(LEN(TEXT(E180,"000000"))=6,LEFT(TEXT(E180,"000000"),2),""),"")</f>
@@ -19385,7 +19412,7 @@
         <v>269</v>
       </c>
       <c r="K180" s="11" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="L180" s="11" t="s">
         <v>59</v>
@@ -19412,7 +19439,7 @@
         <v>63</v>
       </c>
       <c r="AK180" s="1" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="AM180" s="12" t="s">
         <v>65</v>
@@ -19439,16 +19466,16 @@
     </row>
     <row r="181" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A181" s="1" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="C181" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="E181" s="1" t="s">
         <v>192</v>
@@ -19467,7 +19494,7 @@
         <v>195</v>
       </c>
       <c r="K181" s="11" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="L181" s="11" t="s">
         <v>59</v>
@@ -19494,7 +19521,7 @@
         <v>63</v>
       </c>
       <c r="AK181" s="1" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="AM181" s="12" t="n">
         <v>46311</v>
@@ -19521,16 +19548,16 @@
     </row>
     <row r="182" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A182" s="1" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="C182" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="E182" s="1" t="s">
         <v>282</v>
@@ -19549,7 +19576,7 @@
         <v>195</v>
       </c>
       <c r="K182" s="11" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="L182" s="11" t="s">
         <v>59</v>
@@ -19576,7 +19603,7 @@
         <v>63</v>
       </c>
       <c r="AK182" s="1" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="AM182" s="12" t="n">
         <v>46311</v>
@@ -19603,19 +19630,19 @@
     </row>
     <row r="183" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A183" s="1" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="C183" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="F183" s="1" t="str">
         <f aca="false">IF(C183="Singapore",IF(LEN(TEXT(E183,"000000"))=6,LEFT(TEXT(E183,"000000"),2),""),"")</f>
@@ -19631,7 +19658,7 @@
         <v>255</v>
       </c>
       <c r="K183" s="11" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="L183" s="11" t="s">
         <v>59</v>
@@ -19658,7 +19685,7 @@
         <v>63</v>
       </c>
       <c r="AK183" s="1" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="AM183" s="12" t="s">
         <v>65</v>
@@ -19685,23 +19712,23 @@
     </row>
     <row r="184" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A184" s="1" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="C184" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="F184" s="1" t="str">
         <f aca="false">IF(C184="Singapore",IF(LEN(TEXT(E184,"000000"))=6,LEFT(TEXT(E184,"000000"),2),""),"")</f>
         <v>00</v>
       </c>
       <c r="K184" s="11" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="L184" s="11" t="s">
         <v>59</v>
@@ -19728,7 +19755,7 @@
         <v>63</v>
       </c>
       <c r="AK184" s="1" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="AM184" s="12" t="n">
         <v>46311</v>
@@ -19755,35 +19782,35 @@
     </row>
     <row r="185" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A185" s="1" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="C185" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="F185" s="1" t="str">
         <f aca="false">IF(C185="Singapore",IF(LEN(TEXT(E185,"000000"))=6,LEFT(TEXT(E185,"000000"),2),""),"")</f>
         <v>79</v>
       </c>
       <c r="H185" s="1" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="I185" s="1" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="J185" s="1" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="K185" s="11" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="L185" s="11" t="s">
         <v>59</v>
@@ -19810,13 +19837,13 @@
         <v>63</v>
       </c>
       <c r="AK185" s="1" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="AM185" s="12" t="n">
         <v>46311</v>
       </c>
       <c r="AN185" s="1" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="AT185" s="1" t="s">
         <v>66</v>
@@ -19840,10 +19867,10 @@
     </row>
     <row r="186" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A186" s="1" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="C186" s="11" t="s">
         <v>52</v>
@@ -19868,7 +19895,7 @@
         <v>72</v>
       </c>
       <c r="K186" s="11" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="L186" s="11" t="s">
         <v>59</v>
@@ -19895,13 +19922,13 @@
         <v>63</v>
       </c>
       <c r="AK186" s="1" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="AM186" s="12" t="n">
         <v>46311</v>
       </c>
       <c r="AN186" s="1" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="AT186" s="1" t="s">
         <v>66</v>
@@ -19925,19 +19952,19 @@
     </row>
     <row r="187" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A187" s="1" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="C187" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="F187" s="1" t="str">
         <f aca="false">IF(C187="Singapore",IF(LEN(TEXT(E187,"000000"))=6,LEFT(TEXT(E187,"000000"),2),""),"")</f>
@@ -19980,13 +20007,13 @@
         <v>63</v>
       </c>
       <c r="AK187" s="1" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="AM187" s="12" t="n">
         <v>46311</v>
       </c>
       <c r="AN187" s="1" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="AT187" s="1" t="s">
         <v>66</v>
@@ -20010,16 +20037,16 @@
     </row>
     <row r="188" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A188" s="1" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="C188" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="F188" s="1" t="str">
         <f aca="false">IF(C188="Singapore",IF(LEN(TEXT(E188,"000000"))=6,LEFT(TEXT(E188,"000000"),2),""),"")</f>
@@ -20053,7 +20080,7 @@
         <v>63</v>
       </c>
       <c r="AK188" s="1" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="AM188" s="12" t="n">
         <v>46311</v>
@@ -20080,19 +20107,19 @@
     </row>
     <row r="189" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A189" s="1" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="C189" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="F189" s="1" t="str">
         <f aca="false">IF(C189="Singapore",IF(LEN(TEXT(E189,"000000"))=6,LEFT(TEXT(E189,"000000"),2),""),"")</f>
@@ -20108,7 +20135,7 @@
         <v>224</v>
       </c>
       <c r="K189" s="11" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="L189" s="11" t="s">
         <v>59</v>
@@ -20135,7 +20162,7 @@
         <v>63</v>
       </c>
       <c r="AK189" s="1" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="AM189" s="12" t="n">
         <v>46311</v>
@@ -20162,10 +20189,10 @@
     </row>
     <row r="190" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A190" s="1" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="C190" s="11" t="s">
         <v>52</v>
@@ -20217,13 +20244,13 @@
         <v>63</v>
       </c>
       <c r="AK190" s="1" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="AM190" s="12" t="n">
         <v>46311</v>
       </c>
       <c r="AN190" s="1" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="AT190" s="1" t="s">
         <v>66</v>
@@ -20247,16 +20274,16 @@
     </row>
     <row r="191" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A191" s="1" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="C191" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="F191" s="1" t="str">
         <f aca="false">IF(C191="Singapore",IF(LEN(TEXT(E191,"000000"))=6,LEFT(TEXT(E191,"000000"),2),""),"")</f>
@@ -20315,19 +20342,19 @@
     </row>
     <row r="192" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A192" s="1" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="C192" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="F192" s="1" t="str">
         <f aca="false">IF(C192="Singapore",IF(LEN(TEXT(E192,"000000"))=6,LEFT(TEXT(E192,"000000"),2),""),"")</f>
@@ -20368,7 +20395,7 @@
         <v>63</v>
       </c>
       <c r="AK192" s="1" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="AM192" s="12" t="s">
         <v>65</v>
@@ -20395,23 +20422,23 @@
     </row>
     <row r="193" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A193" s="1" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="C193" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="F193" s="1" t="str">
         <f aca="false">IF(C193="Singapore",IF(LEN(TEXT(E193,"000000"))=6,LEFT(TEXT(E193,"000000"),2),""),"")</f>
         <v>00</v>
       </c>
       <c r="K193" s="11" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="L193" s="11" t="s">
         <v>59</v>
@@ -20438,7 +20465,7 @@
         <v>63</v>
       </c>
       <c r="AK193" s="1" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="AM193" s="12" t="n">
         <v>46311</v>
@@ -20465,32 +20492,32 @@
     </row>
     <row r="194" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A194" s="1" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="C194" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="F194" s="1" t="str">
         <f aca="false">IF(C194="Singapore",IF(LEN(TEXT(E194,"000000"))=6,LEFT(TEXT(E194,"000000"),2),""),"")</f>
         <v>79</v>
       </c>
       <c r="H194" s="1" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="I194" s="1" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="J194" s="1" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="K194" s="11"/>
       <c r="L194" s="11" t="s">
@@ -20518,7 +20545,7 @@
         <v>63</v>
       </c>
       <c r="AK194" s="1" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="AM194" s="12" t="n">
         <v>46311</v>
@@ -20545,10 +20572,10 @@
     </row>
     <row r="195" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A195" s="1" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="C195" s="11" t="s">
         <v>52</v>
@@ -20606,7 +20633,7 @@
         <v>46311</v>
       </c>
       <c r="AN195" s="1" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="AT195" s="1" t="s">
         <v>66</v>
@@ -20630,10 +20657,10 @@
     </row>
     <row r="196" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A196" s="1" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="C196" s="11" t="s">
         <v>52</v>
@@ -20685,13 +20712,13 @@
         <v>63</v>
       </c>
       <c r="AK196" s="1" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="AM196" s="12" t="n">
         <v>46311</v>
       </c>
       <c r="AN196" s="1" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="AT196" s="1" t="s">
         <v>66</v>
@@ -20715,19 +20742,19 @@
     </row>
     <row r="197" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A197" s="1" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="C197" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="F197" s="1" t="str">
         <f aca="false">IF(C197="Singapore",IF(LEN(TEXT(E197,"000000"))=6,LEFT(TEXT(E197,"000000"),2),""),"")</f>
@@ -20768,7 +20795,7 @@
         <v>63</v>
       </c>
       <c r="AK197" s="1" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="AM197" s="12" t="n">
         <v>46311</v>
@@ -20795,19 +20822,19 @@
     </row>
     <row r="198" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A198" s="1" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="C198" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="F198" s="1" t="str">
         <f aca="false">IF(C198="Singapore",IF(LEN(TEXT(E198,"000000"))=6,LEFT(TEXT(E198,"000000"),2),""),"")</f>
@@ -20848,13 +20875,13 @@
         <v>63</v>
       </c>
       <c r="AK198" s="1" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="AM198" s="12" t="n">
         <v>46311</v>
       </c>
       <c r="AN198" s="1" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="AT198" s="1" t="s">
         <v>66</v>
@@ -20878,19 +20905,19 @@
     </row>
     <row r="199" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A199" s="1" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="C199" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="F199" s="1" t="str">
         <f aca="false">IF(C199="Singapore",IF(LEN(TEXT(E199,"000000"))=6,LEFT(TEXT(E199,"000000"),2),""),"")</f>
@@ -20931,7 +20958,7 @@
         <v>63</v>
       </c>
       <c r="AK199" s="1" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="AM199" s="12" t="s">
         <v>65</v>
@@ -20958,19 +20985,19 @@
     </row>
     <row r="200" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A200" s="1" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="C200" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="F200" s="1" t="str">
         <f aca="false">IF(C200="Singapore",IF(LEN(TEXT(E200,"000000"))=6,LEFT(TEXT(E200,"000000"),2),""),"")</f>
@@ -21013,13 +21040,13 @@
         <v>63</v>
       </c>
       <c r="AK200" s="1" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="AM200" s="12" t="s">
         <v>65</v>
       </c>
       <c r="AN200" s="1" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="AT200" s="1" t="s">
         <v>66</v>
@@ -21043,32 +21070,32 @@
     </row>
     <row r="201" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A201" s="1" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="C201" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="F201" s="1" t="str">
         <f aca="false">IF(C201="Singapore",IF(LEN(TEXT(E201,"000000"))=6,LEFT(TEXT(E201,"000000"),2),""),"")</f>
         <v>79</v>
       </c>
       <c r="H201" s="1" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="I201" s="1" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="J201" s="1" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="K201" s="11" t="s">
         <v>102</v>
@@ -21098,7 +21125,7 @@
         <v>63</v>
       </c>
       <c r="AK201" s="1" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="AM201" s="12" t="n">
         <v>46311</v>
@@ -21125,19 +21152,19 @@
     </row>
     <row r="202" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A202" s="1" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="C202" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="F202" s="1" t="str">
         <f aca="false">IF(C202="Singapore",IF(LEN(TEXT(E202,"000000"))=6,LEFT(TEXT(E202,"000000"),2),""),"")</f>
@@ -21186,7 +21213,7 @@
         <v>46311</v>
       </c>
       <c r="AN202" s="1" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="AT202" s="1" t="s">
         <v>66</v>
@@ -21210,10 +21237,10 @@
     </row>
     <row r="203" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A203" s="1" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="C203" s="11" t="s">
         <v>52</v>
@@ -21238,7 +21265,7 @@
         <v>72</v>
       </c>
       <c r="K203" s="11" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="L203" s="11" t="s">
         <v>59</v>
@@ -21265,13 +21292,13 @@
         <v>63</v>
       </c>
       <c r="AK203" s="1" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="AM203" s="12" t="n">
         <v>46311</v>
       </c>
       <c r="AN203" s="1" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="AT203" s="1" t="s">
         <v>66</v>
@@ -21295,19 +21322,19 @@
     </row>
     <row r="204" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A204" s="1" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="C204" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="F204" s="1" t="str">
         <f aca="false">IF(C204="Singapore",IF(LEN(TEXT(E204,"000000"))=6,LEFT(TEXT(E204,"000000"),2),""),"")</f>
@@ -21350,7 +21377,7 @@
         <v>63</v>
       </c>
       <c r="AK204" s="1" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="AM204" s="12" t="s">
         <v>65</v>
@@ -21377,10 +21404,10 @@
     </row>
     <row r="205" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A205" s="1" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="C205" s="11" t="s">
         <v>52</v>
@@ -21457,16 +21484,16 @@
     </row>
     <row r="206" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A206" s="1" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="C206" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="E206" s="1" t="s">
         <v>206</v>
@@ -21510,7 +21537,7 @@
         <v>63</v>
       </c>
       <c r="AK206" s="1" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="AM206" s="12" t="n">
         <v>46311</v>
@@ -21537,23 +21564,23 @@
     </row>
     <row r="207" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A207" s="1" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="C207" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="F207" s="1" t="str">
         <f aca="false">IF(C207="Singapore",IF(LEN(TEXT(E207,"000000"))=6,LEFT(TEXT(E207,"000000"),2),""),"")</f>
         <v>00</v>
       </c>
       <c r="K207" s="11" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="L207" s="11" t="s">
         <v>59</v>
@@ -21580,7 +21607,7 @@
         <v>63</v>
       </c>
       <c r="AK207" s="1" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="AM207" s="12" t="n">
         <v>46311</v>
@@ -21607,26 +21634,26 @@
     </row>
     <row r="208" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A208" s="1" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="C208" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="F208" s="1" t="str">
         <f aca="false">IF(C208="Singapore",IF(LEN(TEXT(E208,"000000"))=6,LEFT(TEXT(E208,"000000"),2),""),"")</f>
         <v>82</v>
       </c>
       <c r="H208" s="1" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="I208" s="1" t="s">
         <v>492</v>
@@ -21635,7 +21662,7 @@
         <v>493</v>
       </c>
       <c r="K208" s="11" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="L208" s="11" t="s">
         <v>59</v>
@@ -21662,7 +21689,7 @@
         <v>63</v>
       </c>
       <c r="AK208" s="1" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="AM208" s="12" t="n">
         <v>46311</v>
@@ -21689,10 +21716,10 @@
     </row>
     <row r="209" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A209" s="1" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="C209" s="11" t="s">
         <v>52</v>
@@ -21750,7 +21777,7 @@
         <v>46311</v>
       </c>
       <c r="AN209" s="1" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="AT209" s="1" t="s">
         <v>66</v>
@@ -21774,16 +21801,16 @@
     </row>
     <row r="210" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A210" s="1" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="C210" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="F210" s="1" t="str">
         <f aca="false">IF(C210="Singapore",IF(LEN(TEXT(E210,"000000"))=6,LEFT(TEXT(E210,"000000"),2),""),"")</f>
@@ -21817,7 +21844,7 @@
         <v>63</v>
       </c>
       <c r="AK210" s="1" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="AM210" s="12" t="n">
         <v>46311</v>
@@ -21844,10 +21871,10 @@
     </row>
     <row r="211" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A211" s="1" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="C211" s="11" t="s">
         <v>52</v>
@@ -21905,7 +21932,7 @@
         <v>46311</v>
       </c>
       <c r="AN211" s="1" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="AT211" s="1" t="s">
         <v>66</v>
@@ -21929,19 +21956,19 @@
     </row>
     <row r="212" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A212" s="1" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="C212" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="F212" s="1" t="str">
         <f aca="false">IF(C212="Singapore",IF(LEN(TEXT(E212,"000000"))=6,LEFT(TEXT(E212,"000000"),2),""),"")</f>
@@ -21982,7 +22009,7 @@
         <v>63</v>
       </c>
       <c r="AK212" s="1" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="AM212" s="12" t="s">
         <v>65</v>
@@ -26878,18 +26905,18 @@
         <v>9</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="14" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="B2" s="14" t="s">
         <v>194</v>
@@ -26901,12 +26928,12 @@
         <v>193</v>
       </c>
       <c r="E2" s="14" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="14" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="B3" s="14" t="s">
         <v>194</v>
@@ -26918,12 +26945,12 @@
         <v>193</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="B4" s="14" t="s">
         <v>194</v>
@@ -26935,12 +26962,12 @@
         <v>193</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>194</v>
@@ -26952,12 +26979,12 @@
         <v>193</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="B6" s="14" t="s">
         <v>194</v>
@@ -26969,12 +26996,12 @@
         <v>193</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="B7" s="14" t="s">
         <v>194</v>
@@ -26986,12 +27013,12 @@
         <v>193</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="B8" s="14" t="s">
         <v>239</v>
@@ -27003,12 +27030,12 @@
         <v>238</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="B9" s="14" t="s">
         <v>239</v>
@@ -27020,12 +27047,12 @@
         <v>238</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="B10" s="14" t="s">
         <v>389</v>
@@ -27037,12 +27064,12 @@
         <v>388</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="B11" s="14" t="s">
         <v>389</v>
@@ -27054,12 +27081,12 @@
         <v>388</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="B12" s="14" t="s">
         <v>365</v>
@@ -27071,12 +27098,12 @@
         <v>364</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="B13" s="14" t="s">
         <v>365</v>
@@ -27088,12 +27115,12 @@
         <v>364</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="14" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="B14" s="14" t="s">
         <v>365</v>
@@ -27105,12 +27132,12 @@
         <v>364</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="14" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="B15" s="14" t="s">
         <v>213</v>
@@ -27122,12 +27149,12 @@
         <v>212</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="14" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="B16" s="14" t="s">
         <v>213</v>
@@ -27139,12 +27166,12 @@
         <v>212</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="14" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="B17" s="14" t="s">
         <v>213</v>
@@ -27156,12 +27183,12 @@
         <v>212</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="14" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="B18" s="14" t="s">
         <v>602</v>
@@ -27173,12 +27200,12 @@
         <v>601</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="14" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="B19" s="14" t="s">
         <v>223</v>
@@ -27190,12 +27217,12 @@
         <v>222</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="14" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="B20" s="14" t="s">
         <v>223</v>
@@ -27207,12 +27234,12 @@
         <v>222</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="14" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="B21" s="14" t="s">
         <v>339</v>
@@ -27224,12 +27251,12 @@
         <v>338</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="14" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="B22" s="14" t="s">
         <v>339</v>
@@ -27241,46 +27268,46 @@
         <v>338</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="14" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="D23" s="14" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="14" t="s">
+        <v>1132</v>
+      </c>
+      <c r="B24" s="14" t="s">
+        <v>1129</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>1130</v>
+      </c>
+      <c r="D24" s="14" t="s">
         <v>1131</v>
       </c>
-      <c r="B24" s="14" t="s">
-        <v>1128</v>
-      </c>
-      <c r="C24" s="14" t="s">
-        <v>1129</v>
-      </c>
-      <c r="D24" s="14" t="s">
-        <v>1130</v>
-      </c>
       <c r="E24" s="14" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="14" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="B25" s="14" t="s">
         <v>566</v>
@@ -27292,12 +27319,12 @@
         <v>565</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="14" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="B26" s="14" t="s">
         <v>566</v>
@@ -27309,12 +27336,12 @@
         <v>565</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="14" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="B27" s="14" t="s">
         <v>566</v>
@@ -27326,12 +27353,12 @@
         <v>565</v>
       </c>
       <c r="E27" s="14" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="14" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="B28" s="14" t="s">
         <v>566</v>
@@ -27340,15 +27367,15 @@
         <v>567</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="E28" s="14" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="14" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="B29" s="14" t="s">
         <v>109</v>
@@ -27360,12 +27387,12 @@
         <v>108</v>
       </c>
       <c r="E29" s="14" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="14" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="B30" s="14" t="s">
         <v>109</v>
@@ -27377,12 +27404,12 @@
         <v>108</v>
       </c>
       <c r="E30" s="14" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="14" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="B31" s="14" t="s">
         <v>109</v>
@@ -27391,15 +27418,15 @@
         <v>110</v>
       </c>
       <c r="D31" s="14" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="E31" s="14" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="14" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="B32" s="14" t="s">
         <v>56</v>
@@ -27408,15 +27435,15 @@
         <v>57</v>
       </c>
       <c r="D32" s="14" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="E32" s="14" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="14" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="B33" s="14" t="s">
         <v>56</v>
@@ -27428,12 +27455,12 @@
         <v>55</v>
       </c>
       <c r="E33" s="14" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="14" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="B34" s="14" t="s">
         <v>56</v>
@@ -27445,12 +27472,12 @@
         <v>55</v>
       </c>
       <c r="E34" s="14" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="14" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="B35" s="14" t="s">
         <v>187</v>
@@ -27462,12 +27489,12 @@
         <v>321</v>
       </c>
       <c r="E35" s="14" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="B36" s="14" t="s">
         <v>187</v>
@@ -27479,12 +27506,12 @@
         <v>321</v>
       </c>
       <c r="E36" s="14" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="14" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="B37" s="14" t="s">
         <v>187</v>
@@ -27496,12 +27523,12 @@
         <v>186</v>
       </c>
       <c r="E37" s="14" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="14" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="B38" s="14" t="s">
         <v>187</v>
@@ -27513,12 +27540,12 @@
         <v>186</v>
       </c>
       <c r="E38" s="14" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B39" s="14" t="s">
         <v>519</v>
@@ -27530,12 +27557,12 @@
         <v>518</v>
       </c>
       <c r="E39" s="14" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="14" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B40" s="14" t="s">
         <v>519</v>
@@ -27547,12 +27574,12 @@
         <v>518</v>
       </c>
       <c r="E40" s="14" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="14" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="B41" s="14" t="s">
         <v>519</v>
@@ -27564,12 +27591,12 @@
         <v>518</v>
       </c>
       <c r="E41" s="14" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="14" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="B42" s="14" t="s">
         <v>519</v>
@@ -27581,12 +27608,12 @@
         <v>642</v>
       </c>
       <c r="E42" s="14" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="14" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="B43" s="14" t="s">
         <v>268</v>
@@ -27598,12 +27625,12 @@
         <v>267</v>
       </c>
       <c r="E43" s="14" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="14" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="B44" s="14" t="s">
         <v>268</v>
@@ -27615,12 +27642,12 @@
         <v>267</v>
       </c>
       <c r="E44" s="14" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="14" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="B45" s="14" t="s">
         <v>268</v>
@@ -27632,12 +27659,12 @@
         <v>267</v>
       </c>
       <c r="E45" s="14" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="14" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="B46" s="14" t="s">
         <v>268</v>
@@ -27646,15 +27673,15 @@
         <v>269</v>
       </c>
       <c r="D46" s="14" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="E46" s="14" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="14" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="B47" s="14" t="s">
         <v>157</v>
@@ -27666,12 +27693,12 @@
         <v>156</v>
       </c>
       <c r="E47" s="14" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="14" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="B48" s="14" t="s">
         <v>157</v>
@@ -27683,12 +27710,12 @@
         <v>156</v>
       </c>
       <c r="E48" s="14" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="14" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="B49" s="14" t="s">
         <v>157</v>
@@ -27700,12 +27727,12 @@
         <v>156</v>
       </c>
       <c r="E49" s="14" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="14" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="B50" s="14" t="s">
         <v>165</v>
@@ -27717,12 +27744,12 @@
         <v>164</v>
       </c>
       <c r="E50" s="14" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="14" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="B51" s="14" t="s">
         <v>165</v>
@@ -27734,12 +27761,12 @@
         <v>164</v>
       </c>
       <c r="E51" s="14" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="14" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="B52" s="14" t="s">
         <v>71</v>
@@ -27751,12 +27778,12 @@
         <v>70</v>
       </c>
       <c r="E52" s="14" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="14" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="B53" s="14" t="s">
         <v>71</v>
@@ -27768,12 +27795,12 @@
         <v>70</v>
       </c>
       <c r="E53" s="14" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="14" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="B54" s="14" t="s">
         <v>492</v>
@@ -27785,12 +27812,12 @@
         <v>491</v>
       </c>
       <c r="E54" s="14" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="14" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="B55" s="14" t="s">
         <v>492</v>
@@ -27802,12 +27829,12 @@
         <v>491</v>
       </c>
       <c r="E55" s="14" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="14" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="B56" s="14" t="s">
         <v>492</v>
@@ -27816,15 +27843,15 @@
         <v>493</v>
       </c>
       <c r="D56" s="14" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="E56" s="14" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="14" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="B57" s="14" t="s">
         <v>314</v>
@@ -27836,12 +27863,12 @@
         <v>313</v>
       </c>
       <c r="E57" s="14" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="14" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="B58" s="14" t="s">
         <v>314</v>
@@ -27853,12 +27880,12 @@
         <v>313</v>
       </c>
       <c r="E58" s="14" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="14" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="B59" s="14" t="s">
         <v>174</v>
@@ -27867,15 +27894,15 @@
         <v>175</v>
       </c>
       <c r="D59" s="14" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="E59" s="14" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="14" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="B60" s="14" t="s">
         <v>174</v>
@@ -27887,12 +27914,12 @@
         <v>173</v>
       </c>
       <c r="E60" s="14" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="14" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="B61" s="14" t="s">
         <v>254</v>
@@ -27901,15 +27928,15 @@
         <v>255</v>
       </c>
       <c r="D61" s="14" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="E61" s="14" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="14" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B62" s="14" t="s">
         <v>254</v>
@@ -27918,15 +27945,15 @@
         <v>255</v>
       </c>
       <c r="D62" s="14" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="E62" s="14" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="14" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="B63" s="14" t="s">
         <v>254</v>
@@ -27938,12 +27965,12 @@
         <v>253</v>
       </c>
       <c r="E63" s="14" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="14" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="B64" s="14" t="s">
         <v>254</v>
@@ -27955,12 +27982,12 @@
         <v>253</v>
       </c>
       <c r="E64" s="14" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="14" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="B65" s="14" t="s">
         <v>254</v>
@@ -27972,12 +27999,12 @@
         <v>253</v>
       </c>
       <c r="E65" s="14" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="14" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="B66" s="14" t="s">
         <v>88</v>
@@ -27989,12 +28016,12 @@
         <v>140</v>
       </c>
       <c r="E66" s="14" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="14" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="B67" s="14" t="s">
         <v>88</v>
@@ -28006,12 +28033,12 @@
         <v>140</v>
       </c>
       <c r="E67" s="14" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="14" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="B68" s="14" t="s">
         <v>88</v>
@@ -28023,12 +28050,12 @@
         <v>87</v>
       </c>
       <c r="E68" s="14" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="14" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="B69" s="14" t="s">
         <v>88</v>
@@ -28040,114 +28067,114 @@
         <v>87</v>
       </c>
       <c r="E69" s="14" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="14" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="B70" s="14" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="C70" s="14" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="D70" s="14" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="E70" s="14" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="14" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="B71" s="14" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="C71" s="14" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="D71" s="14" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="E71" s="14" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="14" t="s">
+        <v>1193</v>
+      </c>
+      <c r="B72" s="14" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C72" s="14" t="s">
+        <v>1189</v>
+      </c>
+      <c r="D72" s="14" t="s">
         <v>1192</v>
       </c>
-      <c r="B72" s="14" t="s">
-        <v>1187</v>
-      </c>
-      <c r="C72" s="14" t="s">
-        <v>1188</v>
-      </c>
-      <c r="D72" s="14" t="s">
-        <v>1191</v>
-      </c>
       <c r="E72" s="14" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="14" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="B73" s="14" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="C73" s="14" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="D73" s="14" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="E73" s="14" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="14" t="s">
+        <v>1198</v>
+      </c>
+      <c r="B74" s="14" t="s">
+        <v>1195</v>
+      </c>
+      <c r="C74" s="14" t="s">
+        <v>1196</v>
+      </c>
+      <c r="D74" s="14" t="s">
         <v>1197</v>
       </c>
-      <c r="B74" s="14" t="s">
-        <v>1194</v>
-      </c>
-      <c r="C74" s="14" t="s">
-        <v>1195</v>
-      </c>
-      <c r="D74" s="14" t="s">
-        <v>1196</v>
-      </c>
       <c r="E74" s="14" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="14" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="B75" s="14" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="C75" s="14" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="D75" s="14" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="E75" s="14" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="14" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="B76" s="14" t="s">
         <v>582</v>
@@ -28159,12 +28186,12 @@
         <v>581</v>
       </c>
       <c r="E76" s="14" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="14" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="B77" s="14" t="s">
         <v>582</v>
@@ -28173,83 +28200,83 @@
         <v>583</v>
       </c>
       <c r="D77" s="14" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="E77" s="14" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="14" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="B78" s="14" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="C78" s="14" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="D78" s="14" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="E78" s="14" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="14" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="B79" s="14" t="s">
+        <v>938</v>
+      </c>
+      <c r="C79" s="14" t="s">
+        <v>939</v>
+      </c>
+      <c r="D79" s="14" t="s">
         <v>937</v>
       </c>
-      <c r="C79" s="14" t="s">
-        <v>938</v>
-      </c>
-      <c r="D79" s="14" t="s">
-        <v>936</v>
-      </c>
       <c r="E79" s="14" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="14" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="B80" s="14" t="s">
+        <v>831</v>
+      </c>
+      <c r="C80" s="14" t="s">
+        <v>832</v>
+      </c>
+      <c r="D80" s="14" t="s">
         <v>830</v>
       </c>
-      <c r="C80" s="14" t="s">
-        <v>831</v>
-      </c>
-      <c r="D80" s="14" t="s">
-        <v>829</v>
-      </c>
       <c r="E80" s="14" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="14" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="B81" s="14" t="s">
+        <v>831</v>
+      </c>
+      <c r="C81" s="14" t="s">
+        <v>832</v>
+      </c>
+      <c r="D81" s="14" t="s">
         <v>830</v>
       </c>
-      <c r="C81" s="14" t="s">
-        <v>831</v>
-      </c>
-      <c r="D81" s="14" t="s">
-        <v>829</v>
-      </c>
       <c r="E81" s="14" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="14" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="B82" s="14" t="s">
         <v>165</v>
@@ -28261,12 +28288,12 @@
         <v>480</v>
       </c>
       <c r="E82" s="14" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="14" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="B83" s="14" t="s">
         <v>492</v>
@@ -28275,15 +28302,15 @@
         <v>493</v>
       </c>
       <c r="D83" s="14" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="E83" s="14" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="14" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="B84" s="14" t="s">
         <v>254</v>
@@ -28292,10 +28319,10 @@
         <v>255</v>
       </c>
       <c r="D84" s="14" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="E84" s="14" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
     </row>
   </sheetData>
@@ -28337,7 +28364,7 @@
         <v>14</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F1" s="15" t="s">
         <v>18</v>
@@ -28360,27 +28387,27 @@
         <v>59</v>
       </c>
       <c r="D2" s="16" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="E2" s="16" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="F2" s="16" t="s">
+        <v>1215</v>
+      </c>
+      <c r="G2" s="16" t="s">
         <v>1214</v>
       </c>
-      <c r="G2" s="16" t="s">
-        <v>1213</v>
-      </c>
       <c r="H2" s="16" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="16" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="C3" s="16" t="s">
         <v>197</v>
@@ -28392,69 +28419,69 @@
         <v>66</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="G3" s="16" t="s">
         <v>66</v>
       </c>
       <c r="H3" s="16" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="B4" s="16" t="s">
         <v>414</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="E4" s="16" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="F4" s="16" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="F5" s="16" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="B7" s="16" t="s">
         <v>399</v>
@@ -28465,24 +28492,24 @@
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="B8" s="16" t="s">
         <v>123</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="B9" s="16" t="s">
         <v>102</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28498,45 +28525,45 @@
         <v>589</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="16" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="16" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="16" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="16" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="16" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="16" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="16" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
     </row>
   </sheetData>
@@ -28564,42 +28591,42 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1251</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
     </row>
   </sheetData>
